--- a/Result/profitability/8147.xlsx
+++ b/Result/profitability/8147.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM67"/>
+  <dimension ref="A1:AM68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-2.83</v>
       </c>
       <c r="M2" t="n">
-        <v>0.25375</v>
+        <v>0.2487499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>36.33375</v>
+        <v>35.82625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007500000000000007</v>
+        <v>0.02249999999999994</v>
       </c>
       <c r="N3" t="n">
-        <v>31.77625</v>
+        <v>31.87625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.9</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.04749999999999996</v>
       </c>
       <c r="N4" t="n">
-        <v>30.66875</v>
+        <v>30.31625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1175</v>
+        <v>0.03124999999999997</v>
       </c>
       <c r="N5" t="n">
-        <v>29.28875</v>
+        <v>28.82</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1030,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.99</v>
       </c>
       <c r="M6" t="n">
-        <v>0.22</v>
+        <v>0.17875</v>
       </c>
       <c r="N6" t="n">
-        <v>27.46</v>
+        <v>26.84625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1325</v>
+        <v>0.1425</v>
       </c>
       <c r="N7" t="n">
-        <v>25.53125</v>
+        <v>25.18</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8937,6 +8937,133 @@
       </c>
       <c r="AM67" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>8147</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>523</v>
+      </c>
+      <c r="D68" t="n">
+        <v>336</v>
+      </c>
+      <c r="E68" t="n">
+        <v>187</v>
+      </c>
+      <c r="F68" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="G68" t="n">
+        <v>42</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>8.03%</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>37</v>
+      </c>
+      <c r="K68" t="n">
+        <v>20</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.6675</v>
+      </c>
+      <c r="N68" t="n">
+        <v>38.5625</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="X68" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>-4.469999999999999</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>-0.1109731876861966</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>-0.5897435897435898</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>-0.0947927199191102</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK68" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
